--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8181,10 +8181,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118767815</v>
+        <v>118767767</v>
       </c>
       <c r="B68" t="n">
-        <v>104927</v>
+        <v>91489</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8197,21 +8197,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>224098</v>
+        <v>5836</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8221,13 +8221,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>531929</v>
+        <v>531949</v>
       </c>
       <c r="R68" t="n">
-        <v>6554006</v>
+        <v>6554017</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8293,10 +8293,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118767767</v>
+        <v>118768593</v>
       </c>
       <c r="B69" t="n">
-        <v>91489</v>
+        <v>57306</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8305,38 +8305,52 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5836</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skogalund (Skogalund), Nrk</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>531949</v>
+        <v>532020</v>
       </c>
       <c r="R69" t="n">
-        <v>6554017</v>
+        <v>6553990</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8368,7 +8382,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8378,7 +8392,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8405,10 +8419,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118768593</v>
+        <v>118768493</v>
       </c>
       <c r="B70" t="n">
-        <v>57306</v>
+        <v>91771</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8421,38 +8435,24 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skogalund (Skogalund), Nrk</t>
@@ -8465,7 +8465,7 @@
         <v>6553990</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8531,10 +8531,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118768493</v>
+        <v>118767815</v>
       </c>
       <c r="B71" t="n">
-        <v>91771</v>
+        <v>104927</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8543,25 +8543,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4361</v>
+        <v>224098</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>532020</v>
+        <v>531929</v>
       </c>
       <c r="R71" t="n">
-        <v>6553990</v>
+        <v>6554006</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8181,10 +8181,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118767767</v>
+        <v>118768593</v>
       </c>
       <c r="B68" t="n">
-        <v>91489</v>
+        <v>57306</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8193,38 +8193,52 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5836</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skogalund (Skogalund), Nrk</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>531949</v>
+        <v>532020</v>
       </c>
       <c r="R68" t="n">
-        <v>6554017</v>
+        <v>6553990</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8256,7 +8270,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8266,7 +8280,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8293,10 +8307,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118768593</v>
+        <v>118767767</v>
       </c>
       <c r="B69" t="n">
-        <v>57306</v>
+        <v>91489</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8305,52 +8319,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>5836</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skogalund (Skogalund), Nrk</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532020</v>
+        <v>531949</v>
       </c>
       <c r="R69" t="n">
-        <v>6553990</v>
+        <v>6554017</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8419,10 +8419,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118768493</v>
+        <v>118767815</v>
       </c>
       <c r="B70" t="n">
-        <v>91771</v>
+        <v>104927</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4361</v>
+        <v>224098</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>532020</v>
+        <v>531929</v>
       </c>
       <c r="R70" t="n">
-        <v>6553990</v>
+        <v>6554006</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8531,10 +8531,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118767815</v>
+        <v>118768493</v>
       </c>
       <c r="B71" t="n">
-        <v>104927</v>
+        <v>91771</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8543,25 +8543,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>224098</v>
+        <v>4361</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>531929</v>
+        <v>532020</v>
       </c>
       <c r="R71" t="n">
-        <v>6554006</v>
+        <v>6553990</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8181,10 +8181,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118768593</v>
+        <v>118767767</v>
       </c>
       <c r="B68" t="n">
-        <v>57306</v>
+        <v>91496</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8193,52 +8193,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>5836</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skogalund (Skogalund), Nrk</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532020</v>
+        <v>531949</v>
       </c>
       <c r="R68" t="n">
-        <v>6553990</v>
+        <v>6554017</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8270,7 +8256,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8280,7 +8266,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8307,10 +8293,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118767767</v>
+        <v>118768493</v>
       </c>
       <c r="B69" t="n">
-        <v>91489</v>
+        <v>91778</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8319,25 +8305,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5836</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8347,13 +8333,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>531949</v>
+        <v>532020</v>
       </c>
       <c r="R69" t="n">
-        <v>6554017</v>
+        <v>6553990</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8382,7 +8368,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8392,7 +8378,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8419,10 +8405,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118767815</v>
+        <v>118768593</v>
       </c>
       <c r="B70" t="n">
-        <v>104927</v>
+        <v>57306</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8431,41 +8417,55 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>224098</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skogalund (Skogalund), Nrk</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>531929</v>
+        <v>532020</v>
       </c>
       <c r="R70" t="n">
-        <v>6554006</v>
+        <v>6553990</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8531,10 +8531,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118768493</v>
+        <v>118767815</v>
       </c>
       <c r="B71" t="n">
-        <v>91771</v>
+        <v>104934</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8543,25 +8543,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4361</v>
+        <v>224098</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>532020</v>
+        <v>531929</v>
       </c>
       <c r="R71" t="n">
-        <v>6553990</v>
+        <v>6554006</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8293,10 +8293,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118768493</v>
+        <v>118768593</v>
       </c>
       <c r="B69" t="n">
-        <v>91778</v>
+        <v>57306</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8309,24 +8309,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skogalund (Skogalund), Nrk</t>
@@ -8339,7 +8353,7 @@
         <v>6553990</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8368,7 +8382,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8378,7 +8392,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8405,10 +8419,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118768593</v>
+        <v>118767815</v>
       </c>
       <c r="B70" t="n">
-        <v>57306</v>
+        <v>104934</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8417,55 +8431,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>224098</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skogalund (Skogalund), Nrk</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>532020</v>
+        <v>531929</v>
       </c>
       <c r="R70" t="n">
-        <v>6553990</v>
+        <v>6554006</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8531,10 +8531,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118767815</v>
+        <v>118768493</v>
       </c>
       <c r="B71" t="n">
-        <v>104934</v>
+        <v>91778</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8543,25 +8543,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>224098</v>
+        <v>4361</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>531929</v>
+        <v>532020</v>
       </c>
       <c r="R71" t="n">
-        <v>6554006</v>
+        <v>6553990</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8641,6 +8641,353 @@
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120109225</v>
+      </c>
+      <c r="B72" t="n">
+        <v>86381</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Skogalund, Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>531989</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6553998</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120108890</v>
+      </c>
+      <c r="B73" t="n">
+        <v>89216</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skogalund, Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>531923</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6553990</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120114700</v>
+      </c>
+      <c r="B74" t="n">
+        <v>86350</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>449</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cortinarius fraudulosus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Skogalund, Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>532003</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6553998</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8764,10 +8764,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120108890</v>
+        <v>120114700</v>
       </c>
       <c r="B73" t="n">
-        <v>89216</v>
+        <v>86350</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8776,49 +8776,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1595</v>
+        <v>449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>531923</v>
+        <v>532003</v>
       </c>
       <c r="R73" t="n">
-        <v>6553990</v>
+        <v>6553998</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8848,28 +8837,17 @@
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8888,10 +8866,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120114700</v>
+        <v>120108890</v>
       </c>
       <c r="B74" t="n">
-        <v>86350</v>
+        <v>89216</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8900,38 +8878,49 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>449</v>
+        <v>1595</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>532003</v>
+        <v>531923</v>
       </c>
       <c r="R74" t="n">
-        <v>6553998</v>
+        <v>6553990</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8961,17 +8950,28 @@
           <t>2024-09-30</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8987,6 +8987,340 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120142883</v>
+      </c>
+      <c r="B75" t="n">
+        <v>86350</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>449</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cortinarius fraudulosus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Skogalund, Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6554001</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120140659</v>
+      </c>
+      <c r="B76" t="n">
+        <v>86410</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Skogalund, Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>531937</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6553987</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120140150</v>
+      </c>
+      <c r="B77" t="n">
+        <v>90097</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skogalund, Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>532002</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6553919</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9322,6 +9322,229 @@
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120168686</v>
+      </c>
+      <c r="B78" t="n">
+        <v>86409</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Skogalund, Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>531969</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6553974</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120166523</v>
+      </c>
+      <c r="B79" t="n">
+        <v>86453</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Skogalund, Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>531971</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6553971</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8643,10 +8643,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120109225</v>
+        <v>120108890</v>
       </c>
       <c r="B72" t="n">
-        <v>86381</v>
+        <v>89216</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8655,30 +8655,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>248955</v>
+        <v>1595</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8686,16 +8686,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>531989</v>
+        <v>531923</v>
       </c>
       <c r="R72" t="n">
-        <v>6553998</v>
+        <v>6553990</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8727,7 +8729,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8737,7 +8739,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8746,6 +8748,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8866,10 +8869,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120108890</v>
+        <v>120109225</v>
       </c>
       <c r="B74" t="n">
-        <v>89216</v>
+        <v>86381</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8878,30 +8881,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1595</v>
+        <v>248955</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8909,18 +8912,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>531923</v>
+        <v>531989</v>
       </c>
       <c r="R74" t="n">
-        <v>6553990</v>
+        <v>6553998</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8952,7 +8953,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8962,7 +8963,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8971,7 +8972,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120142883</v>
+        <v>120140150</v>
       </c>
       <c r="B75" t="n">
-        <v>86350</v>
+        <v>90097</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9006,26 +9006,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>449</v>
+        <v>5747</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9039,10 +9039,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>531977</v>
+        <v>532002</v>
       </c>
       <c r="R75" t="n">
-        <v>6554001</v>
+        <v>6553919</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9072,9 +9072,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9203,10 +9213,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120140150</v>
+        <v>120142883</v>
       </c>
       <c r="B77" t="n">
-        <v>90097</v>
+        <v>86350</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9219,26 +9229,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5747</v>
+        <v>449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9252,10 +9262,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>532002</v>
+        <v>531977</v>
       </c>
       <c r="R77" t="n">
-        <v>6553919</v>
+        <v>6554001</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9285,19 +9295,9 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>18:46</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8990,10 +8990,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120140150</v>
+        <v>120140659</v>
       </c>
       <c r="B75" t="n">
-        <v>90097</v>
+        <v>86410</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9002,47 +9002,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5747</v>
+        <v>249228</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Christian</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532002</v>
+        <v>531937</v>
       </c>
       <c r="R75" t="n">
-        <v>6553919</v>
+        <v>6553987</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9072,19 +9063,9 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>18:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9111,10 +9092,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120140659</v>
+        <v>120142883</v>
       </c>
       <c r="B76" t="n">
-        <v>86410</v>
+        <v>86350</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9123,38 +9104,47 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>249228</v>
+        <v>449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>531937</v>
+        <v>531977</v>
       </c>
       <c r="R76" t="n">
-        <v>6553987</v>
+        <v>6554001</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9213,10 +9203,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120142883</v>
+        <v>120140150</v>
       </c>
       <c r="B77" t="n">
-        <v>86350</v>
+        <v>90097</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9229,26 +9219,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>5747</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9262,10 +9252,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>531977</v>
+        <v>532002</v>
       </c>
       <c r="R77" t="n">
-        <v>6554001</v>
+        <v>6553919</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9295,9 +9285,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9545,6 +9545,341 @@
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120276156</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91494</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Skogalund, Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>532026</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6553918</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120272033</v>
+      </c>
+      <c r="B81" t="n">
+        <v>86288</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>426</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gyllenspindling</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cortinarius aureofulvus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Skogalund, Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>532005</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6553947</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120272427</v>
+      </c>
+      <c r="B82" t="n">
+        <v>86354</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Schaeff. : Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Skogalund, Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>531990</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6553976</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8643,10 +8643,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120108890</v>
+        <v>120114700</v>
       </c>
       <c r="B72" t="n">
-        <v>89216</v>
+        <v>86367</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8655,49 +8655,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1595</v>
+        <v>449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>531923</v>
+        <v>532003</v>
       </c>
       <c r="R72" t="n">
-        <v>6553990</v>
+        <v>6553998</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8727,28 +8716,17 @@
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8767,10 +8745,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120114700</v>
+        <v>120109225</v>
       </c>
       <c r="B73" t="n">
-        <v>86350</v>
+        <v>86398</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8783,31 +8761,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>449</v>
+        <v>248955</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>532003</v>
+        <v>531989</v>
       </c>
       <c r="R73" t="n">
         <v>6553998</v>
@@ -8840,9 +8827,19 @@
           <t>2024-09-30</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8869,10 +8866,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120109225</v>
+        <v>120108890</v>
       </c>
       <c r="B74" t="n">
-        <v>86381</v>
+        <v>89233</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8881,30 +8878,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>248955</v>
+        <v>1595</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8912,16 +8909,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>531989</v>
+        <v>531923</v>
       </c>
       <c r="R74" t="n">
-        <v>6553998</v>
+        <v>6553990</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8953,7 +8952,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8963,7 +8962,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8972,6 +8971,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120140659</v>
+        <v>120142883</v>
       </c>
       <c r="B75" t="n">
-        <v>86410</v>
+        <v>86367</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9002,38 +9002,47 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>249228</v>
+        <v>449</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>531937</v>
+        <v>531977</v>
       </c>
       <c r="R75" t="n">
-        <v>6553987</v>
+        <v>6554001</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9092,10 +9101,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120142883</v>
+        <v>120140659</v>
       </c>
       <c r="B76" t="n">
-        <v>86350</v>
+        <v>86427</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9104,47 +9113,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>449</v>
+        <v>249228</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>531977</v>
+        <v>531937</v>
       </c>
       <c r="R76" t="n">
-        <v>6554001</v>
+        <v>6553987</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9206,7 +9206,7 @@
         <v>120140150</v>
       </c>
       <c r="B77" t="n">
-        <v>90097</v>
+        <v>90114</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>120168686</v>
       </c>
       <c r="B78" t="n">
-        <v>86409</v>
+        <v>86426</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>120166523</v>
       </c>
       <c r="B79" t="n">
-        <v>86453</v>
+        <v>86470</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9547,10 +9547,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120276156</v>
+        <v>120272427</v>
       </c>
       <c r="B80" t="n">
-        <v>91494</v>
+        <v>86371</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9563,21 +9563,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4769</v>
+        <v>3624</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius glaucopus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Schaeff. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9587,10 +9587,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>532026</v>
+        <v>531990</v>
       </c>
       <c r="R80" t="n">
-        <v>6553918</v>
+        <v>6553976</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9620,9 +9620,19 @@
           <t>2024-10-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9652,7 +9662,7 @@
         <v>120272033</v>
       </c>
       <c r="B81" t="n">
-        <v>86288</v>
+        <v>86305</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9770,10 +9780,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120272427</v>
+        <v>120276156</v>
       </c>
       <c r="B82" t="n">
-        <v>86354</v>
+        <v>91512</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9786,21 +9796,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3624</v>
+        <v>4769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9810,10 +9820,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>531990</v>
+        <v>532026</v>
       </c>
       <c r="R82" t="n">
-        <v>6553976</v>
+        <v>6553918</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9843,19 +9853,9 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>17:18</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>17:18</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8643,10 +8643,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120114700</v>
+        <v>120109225</v>
       </c>
       <c r="B72" t="n">
-        <v>86367</v>
+        <v>86398</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8659,31 +8659,40 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>449</v>
+        <v>248955</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>532003</v>
+        <v>531989</v>
       </c>
       <c r="R72" t="n">
         <v>6553998</v>
@@ -8716,9 +8725,19 @@
           <t>2024-09-30</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8745,10 +8764,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120109225</v>
+        <v>120108890</v>
       </c>
       <c r="B73" t="n">
-        <v>86398</v>
+        <v>89233</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8757,30 +8776,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>248955</v>
+        <v>1595</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8788,16 +8807,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>531989</v>
+        <v>531923</v>
       </c>
       <c r="R73" t="n">
-        <v>6553998</v>
+        <v>6553990</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8829,7 +8850,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8839,7 +8860,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8848,6 +8869,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8866,10 +8888,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120108890</v>
+        <v>120114700</v>
       </c>
       <c r="B74" t="n">
-        <v>89233</v>
+        <v>86367</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8878,49 +8900,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1595</v>
+        <v>449</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>531923</v>
+        <v>532003</v>
       </c>
       <c r="R74" t="n">
-        <v>6553990</v>
+        <v>6553998</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8950,28 +8961,17 @@
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9547,10 +9547,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120272427</v>
+        <v>120276156</v>
       </c>
       <c r="B80" t="n">
-        <v>86371</v>
+        <v>91512</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9563,21 +9563,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3624</v>
+        <v>4769</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9587,10 +9587,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>531990</v>
+        <v>532026</v>
       </c>
       <c r="R80" t="n">
-        <v>6553976</v>
+        <v>6553918</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9620,19 +9620,9 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>17:18</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>17:18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9780,10 +9770,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120276156</v>
+        <v>120272427</v>
       </c>
       <c r="B82" t="n">
-        <v>91512</v>
+        <v>86371</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9796,21 +9786,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4769</v>
+        <v>3624</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius glaucopus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Schaeff. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9820,10 +9810,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>532026</v>
+        <v>531990</v>
       </c>
       <c r="R82" t="n">
-        <v>6553918</v>
+        <v>6553976</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9853,9 +9843,19 @@
           <t>2024-10-07</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9879,6 +9879,1437 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120392658</v>
+      </c>
+      <c r="B83" t="n">
+        <v>86470</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S83" t="n">
+        <v>75</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120392652</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S84" t="n">
+        <v>75</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120392653</v>
+      </c>
+      <c r="B85" t="n">
+        <v>91901</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S85" t="n">
+        <v>75</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120392663</v>
+      </c>
+      <c r="B86" t="n">
+        <v>90114</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S86" t="n">
+        <v>75</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>120392646</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91851</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>786</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Brandtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hydnellum auratile</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Britzelm.) Maas Geest.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S87" t="n">
+        <v>75</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>120392645</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91850</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S88" t="n">
+        <v>75</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>120392666</v>
+      </c>
+      <c r="B89" t="n">
+        <v>89233</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S89" t="n">
+        <v>75</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120392662</v>
+      </c>
+      <c r="B90" t="n">
+        <v>86427</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S90" t="n">
+        <v>75</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120392667</v>
+      </c>
+      <c r="B91" t="n">
+        <v>89236</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S91" t="n">
+        <v>75</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120392648</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S92" t="n">
+        <v>75</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120392665</v>
+      </c>
+      <c r="B93" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S93" t="n">
+        <v>75</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120392655</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91565</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S94" t="n">
+        <v>75</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>120392643</v>
+      </c>
+      <c r="B95" t="n">
+        <v>90060</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>531977</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6553959</v>
+      </c>
+      <c r="S95" t="n">
+        <v>75</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8643,10 +8643,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120109225</v>
+        <v>120108890</v>
       </c>
       <c r="B72" t="n">
-        <v>86398</v>
+        <v>89233</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8655,30 +8655,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>248955</v>
+        <v>1595</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8686,16 +8686,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>531989</v>
+        <v>531923</v>
       </c>
       <c r="R72" t="n">
-        <v>6553998</v>
+        <v>6553990</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8727,7 +8729,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8737,7 +8739,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8746,6 +8748,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8764,10 +8767,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120108890</v>
+        <v>120114700</v>
       </c>
       <c r="B73" t="n">
-        <v>89233</v>
+        <v>86367</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8776,49 +8779,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1595</v>
+        <v>449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>531923</v>
+        <v>532003</v>
       </c>
       <c r="R73" t="n">
-        <v>6553990</v>
+        <v>6553998</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8848,28 +8840,17 @@
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8888,10 +8869,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120114700</v>
+        <v>120109225</v>
       </c>
       <c r="B74" t="n">
-        <v>86367</v>
+        <v>86398</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8904,31 +8885,40 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>449</v>
+        <v>248955</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>532003</v>
+        <v>531989</v>
       </c>
       <c r="R74" t="n">
         <v>6553998</v>
@@ -8961,9 +8951,19 @@
           <t>2024-09-30</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8990,10 +8990,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120142883</v>
+        <v>120140659</v>
       </c>
       <c r="B75" t="n">
-        <v>86367</v>
+        <v>86427</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9002,47 +9002,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>449</v>
+        <v>249228</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>531977</v>
+        <v>531937</v>
       </c>
       <c r="R75" t="n">
-        <v>6554001</v>
+        <v>6553987</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9101,10 +9092,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120140659</v>
+        <v>120142883</v>
       </c>
       <c r="B76" t="n">
-        <v>86427</v>
+        <v>86367</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9113,38 +9104,47 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>249228</v>
+        <v>449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>531937</v>
+        <v>531977</v>
       </c>
       <c r="R76" t="n">
-        <v>6553987</v>
+        <v>6554001</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9547,10 +9547,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120276156</v>
+        <v>120272033</v>
       </c>
       <c r="B80" t="n">
-        <v>91512</v>
+        <v>86305</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9559,38 +9559,47 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4769</v>
+        <v>426</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>532026</v>
+        <v>532005</v>
       </c>
       <c r="R80" t="n">
-        <v>6553918</v>
+        <v>6553947</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9620,9 +9629,19 @@
           <t>2024-10-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9649,10 +9668,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120272033</v>
+        <v>120276156</v>
       </c>
       <c r="B81" t="n">
-        <v>86305</v>
+        <v>91512</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9661,47 +9680,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>426</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>532005</v>
+        <v>532026</v>
       </c>
       <c r="R81" t="n">
-        <v>6553947</v>
+        <v>6553918</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9731,19 +9741,9 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>16:59</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9882,10 +9882,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120392658</v>
+        <v>120392665</v>
       </c>
       <c r="B83" t="n">
-        <v>86470</v>
+        <v>100194</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9894,34 +9894,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3739</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9992,10 +9993,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120392652</v>
+        <v>120392653</v>
       </c>
       <c r="B84" t="n">
-        <v>91902</v>
+        <v>91901</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10008,21 +10009,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10102,10 +10103,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120392653</v>
+        <v>120392662</v>
       </c>
       <c r="B85" t="n">
-        <v>91901</v>
+        <v>86427</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10114,25 +10115,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5448</v>
+        <v>249228</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10212,10 +10213,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120392663</v>
+        <v>120392645</v>
       </c>
       <c r="B86" t="n">
-        <v>90114</v>
+        <v>91850</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10224,25 +10225,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10322,10 +10323,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120392646</v>
+        <v>120392652</v>
       </c>
       <c r="B87" t="n">
-        <v>91851</v>
+        <v>91902</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10334,25 +10335,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>786</v>
+        <v>5449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brandtaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum auratile</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Britzelm.) Maas Geest.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10432,10 +10433,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120392645</v>
+        <v>120392666</v>
       </c>
       <c r="B88" t="n">
-        <v>91850</v>
+        <v>89233</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10444,25 +10445,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4361</v>
+        <v>1595</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10542,10 +10543,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120392666</v>
+        <v>120392655</v>
       </c>
       <c r="B89" t="n">
-        <v>89233</v>
+        <v>91565</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10558,21 +10559,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1595</v>
+        <v>5836</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10652,10 +10653,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120392662</v>
+        <v>120392648</v>
       </c>
       <c r="B90" t="n">
-        <v>86427</v>
+        <v>91879</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10668,21 +10669,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>249228</v>
+        <v>5964</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10762,10 +10763,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120392667</v>
+        <v>120392658</v>
       </c>
       <c r="B91" t="n">
-        <v>89236</v>
+        <v>86470</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10774,25 +10775,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>245042</v>
+        <v>3739</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10872,10 +10873,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120392648</v>
+        <v>120392643</v>
       </c>
       <c r="B92" t="n">
-        <v>91879</v>
+        <v>90060</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10884,25 +10885,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10982,10 +10983,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120392665</v>
+        <v>120392646</v>
       </c>
       <c r="B93" t="n">
-        <v>100194</v>
+        <v>91851</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10994,35 +10995,34 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>786</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandtaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum auratile</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Britzelm.) Maas Geest.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11093,10 +11093,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120392655</v>
+        <v>120392667</v>
       </c>
       <c r="B94" t="n">
-        <v>91565</v>
+        <v>89236</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11109,21 +11109,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5836</v>
+        <v>245042</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120392643</v>
+        <v>120392663</v>
       </c>
       <c r="B95" t="n">
-        <v>90060</v>
+        <v>90114</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11215,25 +11215,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3286</v>
+        <v>5747</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8643,10 +8643,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120108890</v>
+        <v>120114700</v>
       </c>
       <c r="B72" t="n">
-        <v>89233</v>
+        <v>86367</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8655,49 +8655,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1595</v>
+        <v>449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>531923</v>
+        <v>532003</v>
       </c>
       <c r="R72" t="n">
-        <v>6553990</v>
+        <v>6553998</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8727,28 +8716,17 @@
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8767,10 +8745,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120114700</v>
+        <v>120109225</v>
       </c>
       <c r="B73" t="n">
-        <v>86367</v>
+        <v>86398</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8783,31 +8761,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>449</v>
+        <v>248955</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>532003</v>
+        <v>531989</v>
       </c>
       <c r="R73" t="n">
         <v>6553998</v>
@@ -8840,9 +8827,19 @@
           <t>2024-09-30</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8869,10 +8866,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120109225</v>
+        <v>120108890</v>
       </c>
       <c r="B74" t="n">
-        <v>86398</v>
+        <v>89233</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8881,30 +8878,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>248955</v>
+        <v>1595</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8912,16 +8909,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>531989</v>
+        <v>531923</v>
       </c>
       <c r="R74" t="n">
-        <v>6553998</v>
+        <v>6553990</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8953,7 +8952,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8963,7 +8962,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8972,6 +8971,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120140659</v>
+        <v>120142883</v>
       </c>
       <c r="B75" t="n">
-        <v>86427</v>
+        <v>86367</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9002,38 +9002,47 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>249228</v>
+        <v>449</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>531937</v>
+        <v>531977</v>
       </c>
       <c r="R75" t="n">
-        <v>6553987</v>
+        <v>6554001</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9092,10 +9101,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120142883</v>
+        <v>120140150</v>
       </c>
       <c r="B76" t="n">
-        <v>86367</v>
+        <v>90114</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9108,26 +9117,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>449</v>
+        <v>5747</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9141,10 +9150,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>531977</v>
+        <v>532002</v>
       </c>
       <c r="R76" t="n">
-        <v>6554001</v>
+        <v>6553919</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9174,9 +9183,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9203,10 +9222,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120140150</v>
+        <v>120140659</v>
       </c>
       <c r="B77" t="n">
-        <v>90114</v>
+        <v>86427</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9215,47 +9234,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5747</v>
+        <v>249228</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Christian</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>532002</v>
+        <v>531937</v>
       </c>
       <c r="R77" t="n">
-        <v>6553919</v>
+        <v>6553987</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9285,19 +9295,9 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>18:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9324,10 +9324,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120168686</v>
+        <v>120166523</v>
       </c>
       <c r="B78" t="n">
-        <v>86426</v>
+        <v>86470</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9336,38 +9336,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1988</v>
+        <v>3739</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>531969</v>
+        <v>531971</v>
       </c>
       <c r="R78" t="n">
-        <v>6553974</v>
+        <v>6553971</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9397,9 +9406,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9426,10 +9445,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120166523</v>
+        <v>120168686</v>
       </c>
       <c r="B79" t="n">
-        <v>86470</v>
+        <v>86426</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9438,47 +9457,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3739</v>
+        <v>1988</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>531971</v>
+        <v>531969</v>
       </c>
       <c r="R79" t="n">
-        <v>6553971</v>
+        <v>6553974</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9508,19 +9518,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>17:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9547,10 +9547,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120272033</v>
+        <v>120276156</v>
       </c>
       <c r="B80" t="n">
-        <v>86305</v>
+        <v>91512</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9559,47 +9559,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>426</v>
+        <v>4769</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>532005</v>
+        <v>532026</v>
       </c>
       <c r="R80" t="n">
-        <v>6553947</v>
+        <v>6553918</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9629,19 +9620,9 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>16:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9668,10 +9649,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120276156</v>
+        <v>120272033</v>
       </c>
       <c r="B81" t="n">
-        <v>91512</v>
+        <v>86305</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9680,38 +9661,47 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>426</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>532026</v>
+        <v>532005</v>
       </c>
       <c r="R81" t="n">
-        <v>6553918</v>
+        <v>6553947</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9741,9 +9731,19 @@
           <t>2024-10-07</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9882,10 +9882,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120392665</v>
+        <v>120392643</v>
       </c>
       <c r="B83" t="n">
-        <v>100194</v>
+        <v>90060</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9894,35 +9894,34 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>3286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9993,10 +9992,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120392653</v>
+        <v>120392655</v>
       </c>
       <c r="B84" t="n">
-        <v>91901</v>
+        <v>91565</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10005,25 +10004,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5448</v>
+        <v>5836</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10103,10 +10102,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120392662</v>
+        <v>120392653</v>
       </c>
       <c r="B85" t="n">
-        <v>86427</v>
+        <v>91901</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10115,25 +10114,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>249228</v>
+        <v>5448</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10213,10 +10212,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120392645</v>
+        <v>120392667</v>
       </c>
       <c r="B86" t="n">
-        <v>91850</v>
+        <v>89236</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10225,25 +10224,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>245042</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10323,10 +10322,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120392652</v>
+        <v>120392646</v>
       </c>
       <c r="B87" t="n">
-        <v>91902</v>
+        <v>91851</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10335,25 +10334,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5449</v>
+        <v>786</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Brandtaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum auratile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Britzelm.) Maas Geest.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10433,10 +10432,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120392666</v>
+        <v>120392645</v>
       </c>
       <c r="B88" t="n">
-        <v>89233</v>
+        <v>91850</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10445,25 +10444,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1595</v>
+        <v>4361</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10543,10 +10542,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120392655</v>
+        <v>120392648</v>
       </c>
       <c r="B89" t="n">
-        <v>91565</v>
+        <v>91879</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10559,21 +10558,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5836</v>
+        <v>5964</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10653,10 +10652,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120392648</v>
+        <v>120392652</v>
       </c>
       <c r="B90" t="n">
-        <v>91879</v>
+        <v>91902</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10665,25 +10664,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5964</v>
+        <v>5449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10763,10 +10762,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120392658</v>
+        <v>120392665</v>
       </c>
       <c r="B91" t="n">
-        <v>86470</v>
+        <v>100194</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10775,34 +10774,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3739</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10873,10 +10873,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120392643</v>
+        <v>120392658</v>
       </c>
       <c r="B92" t="n">
-        <v>90060</v>
+        <v>86470</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10889,21 +10889,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3286</v>
+        <v>3739</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10983,10 +10983,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120392646</v>
+        <v>120392663</v>
       </c>
       <c r="B93" t="n">
-        <v>91851</v>
+        <v>90114</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10999,21 +10999,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>786</v>
+        <v>5747</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brandtaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum auratile</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Britzelm.) Maas Geest.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11093,10 +11093,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120392667</v>
+        <v>120392662</v>
       </c>
       <c r="B94" t="n">
-        <v>89236</v>
+        <v>86427</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11109,21 +11109,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>245042</v>
+        <v>249228</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120392663</v>
+        <v>120392666</v>
       </c>
       <c r="B95" t="n">
-        <v>90114</v>
+        <v>89233</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11215,25 +11215,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5747</v>
+        <v>1595</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8990,10 +8990,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120142883</v>
+        <v>120140150</v>
       </c>
       <c r="B75" t="n">
-        <v>86367</v>
+        <v>90114</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9006,26 +9006,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>449</v>
+        <v>5747</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9039,10 +9039,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>531977</v>
+        <v>532002</v>
       </c>
       <c r="R75" t="n">
-        <v>6554001</v>
+        <v>6553919</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9072,9 +9072,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9101,10 +9111,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120140150</v>
+        <v>120142883</v>
       </c>
       <c r="B76" t="n">
-        <v>90114</v>
+        <v>86367</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9117,26 +9127,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5747</v>
+        <v>449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9150,10 +9160,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>532002</v>
+        <v>531977</v>
       </c>
       <c r="R76" t="n">
-        <v>6553919</v>
+        <v>6554001</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9183,19 +9193,9 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>18:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9324,10 +9324,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120166523</v>
+        <v>120168686</v>
       </c>
       <c r="B78" t="n">
-        <v>86470</v>
+        <v>86426</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9336,47 +9336,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3739</v>
+        <v>1988</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>531971</v>
+        <v>531969</v>
       </c>
       <c r="R78" t="n">
-        <v>6553971</v>
+        <v>6553974</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9406,19 +9397,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>17:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9445,10 +9426,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120168686</v>
+        <v>120166523</v>
       </c>
       <c r="B79" t="n">
-        <v>86426</v>
+        <v>86470</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9457,38 +9438,47 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1988</v>
+        <v>3739</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>531969</v>
+        <v>531971</v>
       </c>
       <c r="R79" t="n">
-        <v>6553974</v>
+        <v>6553971</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9518,9 +9508,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9882,10 +9882,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120392643</v>
+        <v>120392667</v>
       </c>
       <c r="B83" t="n">
-        <v>90060</v>
+        <v>89236</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9894,25 +9894,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3286</v>
+        <v>245042</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9992,10 +9992,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120392655</v>
+        <v>120392653</v>
       </c>
       <c r="B84" t="n">
-        <v>91565</v>
+        <v>91901</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10004,25 +10004,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5836</v>
+        <v>5448</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10102,10 +10102,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120392653</v>
+        <v>120392663</v>
       </c>
       <c r="B85" t="n">
-        <v>91901</v>
+        <v>90114</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10114,25 +10114,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5448</v>
+        <v>5747</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10212,10 +10212,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120392667</v>
+        <v>120392646</v>
       </c>
       <c r="B86" t="n">
-        <v>89236</v>
+        <v>91851</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10224,25 +10224,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>245042</v>
+        <v>786</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Brandtaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Hydnellum auratile</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Britzelm.) Maas Geest.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10322,10 +10322,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120392646</v>
+        <v>120392652</v>
       </c>
       <c r="B87" t="n">
-        <v>91851</v>
+        <v>91902</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10334,25 +10334,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>786</v>
+        <v>5449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brandtaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum auratile</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Britzelm.) Maas Geest.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10432,10 +10432,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120392645</v>
+        <v>120392643</v>
       </c>
       <c r="B88" t="n">
-        <v>91850</v>
+        <v>90060</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10448,21 +10448,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4361</v>
+        <v>3286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120392648</v>
+        <v>120392666</v>
       </c>
       <c r="B89" t="n">
-        <v>91879</v>
+        <v>89233</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10558,21 +10558,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5964</v>
+        <v>1595</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120392652</v>
+        <v>120392645</v>
       </c>
       <c r="B90" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10668,21 +10668,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120392665</v>
+        <v>120392662</v>
       </c>
       <c r="B91" t="n">
-        <v>100194</v>
+        <v>86427</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10778,31 +10778,30 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>249228</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10873,10 +10872,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120392658</v>
+        <v>120392665</v>
       </c>
       <c r="B92" t="n">
-        <v>86470</v>
+        <v>100194</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10885,34 +10884,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3739</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10983,10 +10983,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120392663</v>
+        <v>120392658</v>
       </c>
       <c r="B93" t="n">
-        <v>90114</v>
+        <v>86470</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10995,25 +10995,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5747</v>
+        <v>3739</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11093,10 +11093,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120392662</v>
+        <v>120392648</v>
       </c>
       <c r="B94" t="n">
-        <v>86427</v>
+        <v>91879</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11109,21 +11109,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>249228</v>
+        <v>5964</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120392666</v>
+        <v>120392655</v>
       </c>
       <c r="B95" t="n">
-        <v>89233</v>
+        <v>91565</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11219,21 +11219,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1595</v>
+        <v>5836</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8990,10 +8990,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120140150</v>
+        <v>120140659</v>
       </c>
       <c r="B75" t="n">
-        <v>90114</v>
+        <v>86427</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9002,47 +9002,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5747</v>
+        <v>249228</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Christian</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532002</v>
+        <v>531937</v>
       </c>
       <c r="R75" t="n">
-        <v>6553919</v>
+        <v>6553987</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9072,19 +9063,9 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>18:46</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>18:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9222,10 +9203,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120140659</v>
+        <v>120140150</v>
       </c>
       <c r="B77" t="n">
-        <v>86427</v>
+        <v>90114</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9234,38 +9215,47 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>249228</v>
+        <v>5747</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>531937</v>
+        <v>532002</v>
       </c>
       <c r="R77" t="n">
-        <v>6553987</v>
+        <v>6553919</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9295,9 +9285,19 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9324,10 +9324,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120168686</v>
+        <v>120166523</v>
       </c>
       <c r="B78" t="n">
-        <v>86426</v>
+        <v>86470</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9336,38 +9336,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1988</v>
+        <v>3739</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>531969</v>
+        <v>531971</v>
       </c>
       <c r="R78" t="n">
-        <v>6553974</v>
+        <v>6553971</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9397,9 +9406,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9426,10 +9445,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120166523</v>
+        <v>120168686</v>
       </c>
       <c r="B79" t="n">
-        <v>86470</v>
+        <v>86426</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9438,47 +9457,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3739</v>
+        <v>1988</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>531971</v>
+        <v>531969</v>
       </c>
       <c r="R79" t="n">
-        <v>6553971</v>
+        <v>6553974</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9508,19 +9518,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>17:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9547,10 +9547,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120276156</v>
+        <v>120272427</v>
       </c>
       <c r="B80" t="n">
-        <v>91512</v>
+        <v>86371</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9563,21 +9563,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4769</v>
+        <v>3624</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius glaucopus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Schaeff. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9587,10 +9587,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>532026</v>
+        <v>531990</v>
       </c>
       <c r="R80" t="n">
-        <v>6553918</v>
+        <v>6553976</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9620,9 +9620,19 @@
           <t>2024-10-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9649,10 +9659,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120272033</v>
+        <v>120276156</v>
       </c>
       <c r="B81" t="n">
-        <v>86305</v>
+        <v>91512</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9661,47 +9671,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>426</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>532005</v>
+        <v>532026</v>
       </c>
       <c r="R81" t="n">
-        <v>6553947</v>
+        <v>6553918</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9731,19 +9732,9 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>16:59</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9770,10 +9761,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120272427</v>
+        <v>120272033</v>
       </c>
       <c r="B82" t="n">
-        <v>86371</v>
+        <v>86305</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9782,38 +9773,47 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3624</v>
+        <v>426</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>531990</v>
+        <v>532005</v>
       </c>
       <c r="R82" t="n">
-        <v>6553976</v>
+        <v>6553947</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9882,10 +9882,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120392667</v>
+        <v>120392655</v>
       </c>
       <c r="B83" t="n">
-        <v>89236</v>
+        <v>91565</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9898,21 +9898,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>245042</v>
+        <v>5836</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10102,10 +10102,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120392663</v>
+        <v>120392652</v>
       </c>
       <c r="B85" t="n">
-        <v>90114</v>
+        <v>91902</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10114,25 +10114,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5747</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10322,10 +10322,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120392652</v>
+        <v>120392662</v>
       </c>
       <c r="B87" t="n">
-        <v>91902</v>
+        <v>86427</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10334,25 +10334,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5449</v>
+        <v>249228</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10432,10 +10432,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120392643</v>
+        <v>120392645</v>
       </c>
       <c r="B88" t="n">
-        <v>90060</v>
+        <v>91850</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10448,21 +10448,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3286</v>
+        <v>4361</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120392666</v>
+        <v>120392648</v>
       </c>
       <c r="B89" t="n">
-        <v>89233</v>
+        <v>91879</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10558,21 +10558,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1595</v>
+        <v>5964</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120392645</v>
+        <v>120392663</v>
       </c>
       <c r="B90" t="n">
-        <v>91850</v>
+        <v>90114</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10664,25 +10664,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120392662</v>
+        <v>120392666</v>
       </c>
       <c r="B91" t="n">
-        <v>86427</v>
+        <v>89233</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10778,21 +10778,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>249228</v>
+        <v>1595</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10872,10 +10872,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120392665</v>
+        <v>120392643</v>
       </c>
       <c r="B92" t="n">
-        <v>100194</v>
+        <v>90060</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10884,35 +10884,34 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222498</v>
+        <v>3286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10983,10 +10982,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120392658</v>
+        <v>120392665</v>
       </c>
       <c r="B93" t="n">
-        <v>86470</v>
+        <v>100194</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10995,34 +10994,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3739</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11093,10 +11093,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120392648</v>
+        <v>120392667</v>
       </c>
       <c r="B94" t="n">
-        <v>91879</v>
+        <v>89236</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11109,21 +11109,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5964</v>
+        <v>245042</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120392655</v>
+        <v>120392658</v>
       </c>
       <c r="B95" t="n">
-        <v>91565</v>
+        <v>86470</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11215,25 +11215,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5836</v>
+        <v>3739</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -8643,10 +8643,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120114700</v>
+        <v>120108890</v>
       </c>
       <c r="B72" t="n">
-        <v>86367</v>
+        <v>89233</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8655,38 +8655,49 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>449</v>
+        <v>1595</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>532003</v>
+        <v>531923</v>
       </c>
       <c r="R72" t="n">
-        <v>6553998</v>
+        <v>6553990</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8716,17 +8727,28 @@
           <t>2024-09-30</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8745,10 +8767,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120109225</v>
+        <v>120114700</v>
       </c>
       <c r="B73" t="n">
-        <v>86398</v>
+        <v>86367</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8761,40 +8783,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>248955</v>
+        <v>449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kauffman</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>531989</v>
+        <v>532003</v>
       </c>
       <c r="R73" t="n">
         <v>6553998</v>
@@ -8827,19 +8840,9 @@
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:34</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8866,10 +8869,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120108890</v>
+        <v>120109225</v>
       </c>
       <c r="B74" t="n">
-        <v>89233</v>
+        <v>86398</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8878,30 +8881,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1595</v>
+        <v>248955</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8909,18 +8912,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>531923</v>
+        <v>531989</v>
       </c>
       <c r="R74" t="n">
-        <v>6553990</v>
+        <v>6553998</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8952,7 +8953,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8962,7 +8963,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8971,7 +8972,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9324,10 +9324,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120166523</v>
+        <v>120168686</v>
       </c>
       <c r="B78" t="n">
-        <v>86470</v>
+        <v>86426</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9336,47 +9336,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3739</v>
+        <v>1988</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>531971</v>
+        <v>531969</v>
       </c>
       <c r="R78" t="n">
-        <v>6553971</v>
+        <v>6553974</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9406,19 +9397,9 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>17:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9445,10 +9426,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120168686</v>
+        <v>120166523</v>
       </c>
       <c r="B79" t="n">
-        <v>86426</v>
+        <v>86470</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9457,38 +9438,47 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1988</v>
+        <v>3739</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>531969</v>
+        <v>531971</v>
       </c>
       <c r="R79" t="n">
-        <v>6553974</v>
+        <v>6553971</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9518,9 +9508,19 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9547,10 +9547,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120272427</v>
+        <v>120272033</v>
       </c>
       <c r="B80" t="n">
-        <v>86371</v>
+        <v>86305</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9559,38 +9559,47 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3624</v>
+        <v>426</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>531990</v>
+        <v>532005</v>
       </c>
       <c r="R80" t="n">
-        <v>6553976</v>
+        <v>6553947</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9622,7 +9631,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9632,7 +9641,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9761,10 +9770,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120272033</v>
+        <v>120272427</v>
       </c>
       <c r="B82" t="n">
-        <v>86305</v>
+        <v>86371</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9773,47 +9782,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>426</v>
+        <v>3624</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Cortinarius glaucopus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff. : Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Skogalund, Skogalund, Nrk</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>532005</v>
+        <v>531990</v>
       </c>
       <c r="R82" t="n">
-        <v>6553947</v>
+        <v>6553976</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9882,10 +9882,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120392655</v>
+        <v>120392662</v>
       </c>
       <c r="B83" t="n">
-        <v>91565</v>
+        <v>86427</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9898,21 +9898,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5836</v>
+        <v>249228</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9992,10 +9992,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120392653</v>
+        <v>120392648</v>
       </c>
       <c r="B84" t="n">
-        <v>91901</v>
+        <v>91879</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10004,25 +10004,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5448</v>
+        <v>5964</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10102,10 +10102,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120392652</v>
+        <v>120392653</v>
       </c>
       <c r="B85" t="n">
-        <v>91902</v>
+        <v>91901</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10212,10 +10212,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120392646</v>
+        <v>120392666</v>
       </c>
       <c r="B86" t="n">
-        <v>91851</v>
+        <v>89233</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10224,25 +10224,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>786</v>
+        <v>1595</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brandtaggsvamp</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum auratile</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Britzelm.) Maas Geest.</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10322,10 +10322,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120392662</v>
+        <v>120392646</v>
       </c>
       <c r="B87" t="n">
-        <v>86427</v>
+        <v>91851</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10334,25 +10334,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>249228</v>
+        <v>786</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Brandtaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hydnellum auratile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Britzelm.) Maas Geest.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10432,10 +10432,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120392645</v>
+        <v>120392658</v>
       </c>
       <c r="B88" t="n">
-        <v>91850</v>
+        <v>86470</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10448,21 +10448,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4361</v>
+        <v>3739</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120392648</v>
+        <v>120392645</v>
       </c>
       <c r="B89" t="n">
-        <v>91879</v>
+        <v>91850</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10554,25 +10554,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120392666</v>
+        <v>120392665</v>
       </c>
       <c r="B91" t="n">
-        <v>89233</v>
+        <v>100194</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10778,30 +10778,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1595</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10872,10 +10873,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120392643</v>
+        <v>120392667</v>
       </c>
       <c r="B92" t="n">
-        <v>90060</v>
+        <v>89236</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10884,25 +10885,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3286</v>
+        <v>245042</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10982,10 +10983,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120392665</v>
+        <v>120392652</v>
       </c>
       <c r="B93" t="n">
-        <v>100194</v>
+        <v>91902</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10994,35 +10995,34 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>5449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11093,10 +11093,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120392667</v>
+        <v>120392643</v>
       </c>
       <c r="B94" t="n">
-        <v>89236</v>
+        <v>90060</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11105,25 +11105,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>245042</v>
+        <v>3286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120392658</v>
+        <v>120392655</v>
       </c>
       <c r="B95" t="n">
-        <v>86470</v>
+        <v>91565</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11215,25 +11215,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3739</v>
+        <v>5836</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11311,6 +11311,1416 @@
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>120631985</v>
+      </c>
+      <c r="B96" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>532031</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6553884</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>120632006</v>
+      </c>
+      <c r="B97" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>531943</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6554029</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>120631956</v>
+      </c>
+      <c r="B98" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>531923</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6554006</v>
+      </c>
+      <c r="S98" t="n">
+        <v>25</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>120631955</v>
+      </c>
+      <c r="B99" t="n">
+        <v>91901</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>531923</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6554006</v>
+      </c>
+      <c r="S99" t="n">
+        <v>25</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>120631997</v>
+      </c>
+      <c r="B100" t="n">
+        <v>86371</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Schaeff. : Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>531967</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6553983</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>120632000</v>
+      </c>
+      <c r="B101" t="n">
+        <v>90060</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>531967</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6553983</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>120631962</v>
+      </c>
+      <c r="B102" t="n">
+        <v>91870</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>531923</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6554006</v>
+      </c>
+      <c r="S102" t="n">
+        <v>25</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>120632001</v>
+      </c>
+      <c r="B103" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>531967</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6553983</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>120632022</v>
+      </c>
+      <c r="B104" t="n">
+        <v>90060</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>531943</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6554029</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>120632019</v>
+      </c>
+      <c r="B105" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>531943</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6554029</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>120631958</v>
+      </c>
+      <c r="B106" t="n">
+        <v>89233</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>531923</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6554006</v>
+      </c>
+      <c r="S106" t="n">
+        <v>25</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>120631970</v>
+      </c>
+      <c r="B107" t="n">
+        <v>91512</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>531957</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6553906</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>120631965</v>
+      </c>
+      <c r="B108" t="n">
+        <v>86367</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>449</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Cortinarius fraudulosus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Skogalund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>531923</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6554006</v>
+      </c>
+      <c r="S108" t="n">
+        <v>25</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18289-2019 artfynd.xlsx
+++ b/artfynd/A 18289-2019 artfynd.xlsx
@@ -12726,7 +12726,7 @@
         <v>127020511</v>
       </c>
       <c r="B109" t="n">
-        <v>92547</v>
+        <v>92621</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12830,32 +12830,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127020532</v>
+        <v>127020515</v>
       </c>
       <c r="B110" t="n">
-        <v>90767</v>
+        <v>92603</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>256335</v>
+        <v>4362</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12865,13 +12865,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>531930</v>
+        <v>531946</v>
       </c>
       <c r="R110" t="n">
-        <v>6553980</v>
+        <v>6553988</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12937,32 +12937,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127020515</v>
+        <v>127020532</v>
       </c>
       <c r="B111" t="n">
-        <v>92529</v>
+        <v>90841</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4362</v>
+        <v>256335</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12972,13 +12972,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>531946</v>
+        <v>531930</v>
       </c>
       <c r="R111" t="n">
-        <v>6553988</v>
+        <v>6553980</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13047,7 +13047,7 @@
         <v>127020541</v>
       </c>
       <c r="B112" t="n">
-        <v>92527</v>
+        <v>92601</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13151,32 +13151,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127020505</v>
+        <v>127021219</v>
       </c>
       <c r="B113" t="n">
-        <v>92563</v>
+        <v>90086</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5449</v>
+        <v>1595</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>531946</v>
+        <v>532001</v>
       </c>
       <c r="R113" t="n">
-        <v>6553988</v>
+        <v>6553959</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13221,7 +13221,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13258,32 +13258,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127021219</v>
+        <v>127020505</v>
       </c>
       <c r="B114" t="n">
-        <v>89965</v>
+        <v>92637</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1595</v>
+        <v>5449</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>532001</v>
+        <v>531946</v>
       </c>
       <c r="R114" t="n">
-        <v>6553959</v>
+        <v>6553988</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13368,7 +13368,7 @@
         <v>127020546</v>
       </c>
       <c r="B115" t="n">
-        <v>92528</v>
+        <v>92602</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>127020566</v>
       </c>
       <c r="B116" t="n">
-        <v>92239</v>
+        <v>92313</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>127118803</v>
       </c>
       <c r="B117" t="n">
-        <v>92561</v>
+        <v>92635</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>127117654</v>
       </c>
       <c r="B118" t="n">
-        <v>92547</v>
+        <v>92621</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
